--- a/backend/data/financials_by_company/1260.TWO.xlsx
+++ b/backend/data/financials_by_company/1260.TWO.xlsx
@@ -647,546 +647,546 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>661800</v>
+        <v>248822.87994</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2</v>
+        <v>0.22336</v>
       </c>
       <c r="D2" t="n">
-        <v>306543000</v>
+        <v>400865000</v>
       </c>
       <c r="E2" t="n">
-        <v>3309000</v>
+        <v>1114000</v>
       </c>
       <c r="F2" t="n">
-        <v>3309000</v>
+        <v>1114000</v>
       </c>
       <c r="G2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="H2" t="n">
-        <v>112742000</v>
+        <v>101578000</v>
       </c>
       <c r="I2" t="n">
-        <v>4592338000</v>
+        <v>3997799000</v>
       </c>
       <c r="J2" t="n">
-        <v>309852000</v>
+        <v>401979000</v>
       </c>
       <c r="K2" t="n">
-        <v>197110000</v>
+        <v>300401000</v>
       </c>
       <c r="L2" t="n">
-        <v>-78646000</v>
+        <v>-28073000</v>
       </c>
       <c r="M2" t="n">
-        <v>81258000</v>
+        <v>28687000</v>
       </c>
       <c r="N2" t="n">
-        <v>2612000</v>
+        <v>614000</v>
       </c>
       <c r="O2" t="n">
-        <v>30227800</v>
+        <v>210158822.87994</v>
       </c>
       <c r="P2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5200403000</v>
+        <v>4390758000</v>
       </c>
       <c r="R2" t="n">
-        <v>102316000</v>
+        <v>102637000</v>
       </c>
       <c r="S2" t="n">
         <v>102098000</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.07</v>
+      </c>
       <c r="V2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="W2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="Z2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="AA2" t="n">
-        <v>32875000</v>
+        <v>211024000</v>
       </c>
       <c r="AB2" t="n">
-        <v>82977000</v>
+        <v>60690000</v>
       </c>
       <c r="AC2" t="n">
-        <v>115852000</v>
+        <v>271714000</v>
       </c>
       <c r="AD2" t="n">
-        <v>11137000</v>
+        <v>25450000</v>
       </c>
       <c r="AE2" t="n">
-        <v>3309000</v>
+        <v>1114000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3309000</v>
+        <v>-1114000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-78646000</v>
+        <v>-28073000</v>
       </c>
       <c r="AH2" t="n">
-        <v>81258000</v>
+        <v>28687000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2612000</v>
+        <v>614000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>167472000</v>
+        <v>260536000</v>
       </c>
       <c r="AK2" t="n">
-        <v>608065000</v>
+        <v>392959000</v>
       </c>
       <c r="AL2" t="n">
-        <v>12997000</v>
+        <v>13956000</v>
       </c>
       <c r="AM2" t="n">
-        <v>595068000</v>
+        <v>379003000</v>
       </c>
       <c r="AN2" t="n">
-        <v>405545000</v>
+        <v>212704000</v>
       </c>
       <c r="AO2" t="n">
-        <v>189523000</v>
+        <v>166299000</v>
       </c>
       <c r="AP2" t="n">
-        <v>775537000</v>
+        <v>653495000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4592338000</v>
+        <v>3997799000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5367875000</v>
+        <v>4651294000</v>
       </c>
       <c r="AS2" t="n">
-        <v>5367875000</v>
+        <v>4651294000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1542365.357641</v>
+        <v>-505509.903465</v>
       </c>
       <c r="C3" t="n">
-        <v>0.227186</v>
+        <v>0.232205</v>
       </c>
       <c r="D3" t="n">
-        <v>446306000</v>
+        <v>486029000</v>
       </c>
       <c r="E3" t="n">
-        <v>-6789000</v>
+        <v>-2177000</v>
       </c>
       <c r="F3" t="n">
-        <v>-6789000</v>
+        <v>-2177000</v>
       </c>
       <c r="G3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="H3" t="n">
-        <v>105759000</v>
+        <v>104231000</v>
       </c>
       <c r="I3" t="n">
-        <v>4403033000</v>
+        <v>4267958000</v>
       </c>
       <c r="J3" t="n">
-        <v>439517000</v>
+        <v>483852000</v>
       </c>
       <c r="K3" t="n">
-        <v>333758000</v>
+        <v>379621000</v>
       </c>
       <c r="L3" t="n">
-        <v>-66762000</v>
+        <v>-31972000</v>
       </c>
       <c r="M3" t="n">
-        <v>69261000</v>
+        <v>33530000</v>
       </c>
       <c r="N3" t="n">
-        <v>2499000</v>
+        <v>1558000</v>
       </c>
       <c r="O3" t="n">
-        <v>209653634.642359</v>
+        <v>267398490.096535</v>
       </c>
       <c r="P3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4900380000</v>
+        <v>4720862000</v>
       </c>
       <c r="R3" t="n">
-        <v>102717085</v>
+        <v>102651000</v>
       </c>
       <c r="S3" t="n">
         <v>102098000</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="W3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="Z3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="AA3" t="n">
-        <v>204407000</v>
+        <v>265727000</v>
       </c>
       <c r="AB3" t="n">
-        <v>60090000</v>
+        <v>80364000</v>
       </c>
       <c r="AC3" t="n">
-        <v>264497000</v>
+        <v>346091000</v>
       </c>
       <c r="AD3" t="n">
-        <v>26052000</v>
+        <v>46639000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6789000</v>
+        <v>-2177000</v>
       </c>
       <c r="AF3" t="n">
-        <v>6789000</v>
+        <v>2177000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-66762000</v>
+        <v>-31972000</v>
       </c>
       <c r="AH3" t="n">
-        <v>69261000</v>
+        <v>33530000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2499000</v>
+        <v>1558000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>295821000</v>
+        <v>338729000</v>
       </c>
       <c r="AK3" t="n">
-        <v>497347000</v>
+        <v>452904000</v>
       </c>
       <c r="AL3" t="n">
-        <v>13506000</v>
+        <v>11717000</v>
       </c>
       <c r="AM3" t="n">
-        <v>483841000</v>
+        <v>441187000</v>
       </c>
       <c r="AN3" t="n">
-        <v>303796000</v>
+        <v>251648000</v>
       </c>
       <c r="AO3" t="n">
-        <v>180045000</v>
+        <v>189539000</v>
       </c>
       <c r="AP3" t="n">
-        <v>793168000</v>
+        <v>791633000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4403033000</v>
+        <v>4267958000</v>
       </c>
       <c r="AR3" t="n">
-        <v>5196201000</v>
+        <v>5059591000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5196201000</v>
+        <v>5059591000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-505509.903465</v>
+        <v>-1542365.357641</v>
       </c>
       <c r="C4" t="n">
-        <v>0.232205</v>
+        <v>0.227186</v>
       </c>
       <c r="D4" t="n">
-        <v>486029000</v>
+        <v>446306000</v>
       </c>
       <c r="E4" t="n">
-        <v>-2177000</v>
+        <v>-6789000</v>
       </c>
       <c r="F4" t="n">
-        <v>-2177000</v>
+        <v>-6789000</v>
       </c>
       <c r="G4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="H4" t="n">
-        <v>104231000</v>
+        <v>105759000</v>
       </c>
       <c r="I4" t="n">
-        <v>4267958000</v>
+        <v>4403033000</v>
       </c>
       <c r="J4" t="n">
-        <v>483852000</v>
+        <v>439517000</v>
       </c>
       <c r="K4" t="n">
-        <v>379621000</v>
+        <v>333758000</v>
       </c>
       <c r="L4" t="n">
-        <v>-31972000</v>
+        <v>-66762000</v>
       </c>
       <c r="M4" t="n">
-        <v>33530000</v>
+        <v>69261000</v>
       </c>
       <c r="N4" t="n">
-        <v>1558000</v>
+        <v>2499000</v>
       </c>
       <c r="O4" t="n">
-        <v>267398490.096535</v>
+        <v>209653634.642359</v>
       </c>
       <c r="P4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4720862000</v>
+        <v>4900380000</v>
       </c>
       <c r="R4" t="n">
-        <v>102651000</v>
+        <v>102717085</v>
       </c>
       <c r="S4" t="n">
         <v>102098000</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="W4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="Z4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="AA4" t="n">
-        <v>265727000</v>
+        <v>204407000</v>
       </c>
       <c r="AB4" t="n">
-        <v>80364000</v>
+        <v>60090000</v>
       </c>
       <c r="AC4" t="n">
-        <v>346091000</v>
+        <v>264497000</v>
       </c>
       <c r="AD4" t="n">
-        <v>46639000</v>
+        <v>26052000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2177000</v>
+        <v>-6789000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2177000</v>
+        <v>6789000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-31972000</v>
+        <v>-66762000</v>
       </c>
       <c r="AH4" t="n">
-        <v>33530000</v>
+        <v>69261000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1558000</v>
+        <v>2499000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>338729000</v>
+        <v>295821000</v>
       </c>
       <c r="AK4" t="n">
-        <v>452904000</v>
+        <v>497347000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11717000</v>
+        <v>13506000</v>
       </c>
       <c r="AM4" t="n">
-        <v>441187000</v>
+        <v>483841000</v>
       </c>
       <c r="AN4" t="n">
-        <v>251648000</v>
+        <v>303796000</v>
       </c>
       <c r="AO4" t="n">
-        <v>189539000</v>
+        <v>180045000</v>
       </c>
       <c r="AP4" t="n">
-        <v>791633000</v>
+        <v>793168000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4267958000</v>
+        <v>4403033000</v>
       </c>
       <c r="AR4" t="n">
-        <v>5059591000</v>
+        <v>5196201000</v>
       </c>
       <c r="AS4" t="n">
-        <v>5059591000</v>
+        <v>5196201000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>248822.87994</v>
+        <v>661800</v>
       </c>
       <c r="C5" t="n">
-        <v>0.22336</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>400865000</v>
+        <v>306543000</v>
       </c>
       <c r="E5" t="n">
-        <v>1114000</v>
+        <v>3309000</v>
       </c>
       <c r="F5" t="n">
-        <v>1114000</v>
+        <v>3309000</v>
       </c>
       <c r="G5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="H5" t="n">
-        <v>101578000</v>
+        <v>112742000</v>
       </c>
       <c r="I5" t="n">
-        <v>3997799000</v>
+        <v>4592338000</v>
       </c>
       <c r="J5" t="n">
-        <v>401979000</v>
+        <v>309852000</v>
       </c>
       <c r="K5" t="n">
-        <v>300401000</v>
+        <v>197110000</v>
       </c>
       <c r="L5" t="n">
-        <v>-28073000</v>
+        <v>-78646000</v>
       </c>
       <c r="M5" t="n">
-        <v>28687000</v>
+        <v>81258000</v>
       </c>
       <c r="N5" t="n">
-        <v>614000</v>
+        <v>2612000</v>
       </c>
       <c r="O5" t="n">
-        <v>210158822.87994</v>
+        <v>30227800</v>
       </c>
       <c r="P5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="Q5" t="n">
-        <v>4390758000</v>
+        <v>5200403000</v>
       </c>
       <c r="R5" t="n">
-        <v>102637000</v>
+        <v>102316000</v>
       </c>
       <c r="S5" t="n">
         <v>102098000</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.07</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="W5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="Z5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="AA5" t="n">
-        <v>211024000</v>
+        <v>32875000</v>
       </c>
       <c r="AB5" t="n">
-        <v>60690000</v>
+        <v>82977000</v>
       </c>
       <c r="AC5" t="n">
-        <v>271714000</v>
+        <v>115852000</v>
       </c>
       <c r="AD5" t="n">
-        <v>25450000</v>
+        <v>11137000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1114000</v>
+        <v>3309000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1114000</v>
+        <v>-3309000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-28073000</v>
+        <v>-78646000</v>
       </c>
       <c r="AH5" t="n">
-        <v>28687000</v>
+        <v>81258000</v>
       </c>
       <c r="AI5" t="n">
-        <v>614000</v>
+        <v>2612000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>260536000</v>
+        <v>167472000</v>
       </c>
       <c r="AK5" t="n">
-        <v>392959000</v>
+        <v>608065000</v>
       </c>
       <c r="AL5" t="n">
-        <v>13956000</v>
+        <v>12997000</v>
       </c>
       <c r="AM5" t="n">
-        <v>379003000</v>
+        <v>595068000</v>
       </c>
       <c r="AN5" t="n">
-        <v>212704000</v>
+        <v>405545000</v>
       </c>
       <c r="AO5" t="n">
-        <v>166299000</v>
+        <v>189523000</v>
       </c>
       <c r="AP5" t="n">
-        <v>653495000</v>
+        <v>775537000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3997799000</v>
+        <v>4592338000</v>
       </c>
       <c r="AR5" t="n">
-        <v>4651294000</v>
+        <v>5367875000</v>
       </c>
       <c r="AS5" t="n">
-        <v>4651294000</v>
+        <v>5367875000</v>
       </c>
     </row>
   </sheetData>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>102098000</v>
@@ -1501,40 +1501,40 @@
         <v>102098000</v>
       </c>
       <c r="D2" t="n">
-        <v>1070220000</v>
+        <v>1342591000</v>
       </c>
       <c r="E2" t="n">
-        <v>1687599000</v>
+        <v>1608028000</v>
       </c>
       <c r="F2" t="n">
-        <v>2316332000</v>
+        <v>2169690000</v>
       </c>
       <c r="G2" t="n">
-        <v>3982053000</v>
+        <v>3768564000</v>
       </c>
       <c r="H2" t="n">
-        <v>1126026000</v>
+        <v>1113195000</v>
       </c>
       <c r="I2" t="n">
-        <v>2316332000</v>
+        <v>2169690000</v>
       </c>
       <c r="J2" t="n">
-        <v>25030000</v>
+        <v>10707000</v>
       </c>
       <c r="K2" t="n">
-        <v>2319484000</v>
+        <v>2171243000</v>
       </c>
       <c r="L2" t="n">
-        <v>2448284000</v>
+        <v>2328604000</v>
       </c>
       <c r="M2" t="n">
-        <v>2319484000</v>
+        <v>2171243000</v>
       </c>
       <c r="N2" t="n">
-        <v>2319484000</v>
+        <v>2171243000</v>
       </c>
       <c r="O2" t="n">
-        <v>687811000</v>
+        <v>634781000</v>
       </c>
       <c r="P2" t="n">
         <v>345544000</v>
@@ -1546,129 +1546,127 @@
         <v>1020982000</v>
       </c>
       <c r="S2" t="n">
-        <v>2149434000</v>
+        <v>2045221000</v>
       </c>
       <c r="T2" t="n">
-        <v>154711000</v>
+        <v>195230000</v>
       </c>
       <c r="U2" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1687000</v>
-      </c>
+        <v>2476000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>2721000</v>
+        <v>25201000</v>
       </c>
       <c r="X2" t="n">
-        <v>149183000</v>
+        <v>167553000</v>
       </c>
       <c r="Y2" t="n">
-        <v>20383000</v>
+        <v>10192000</v>
       </c>
       <c r="Z2" t="n">
-        <v>128800000</v>
+        <v>157361000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1994723000</v>
+        <v>1849991000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1854000</v>
+        <v>2144000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1538416000</v>
+        <v>1440475000</v>
       </c>
       <c r="AD2" t="n">
-        <v>4647000</v>
+        <v>515000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1533769000</v>
+        <v>1439960000</v>
       </c>
       <c r="AF2" t="n">
-        <v>422834000</v>
+        <v>380180000</v>
       </c>
       <c r="AG2" t="n">
-        <v>170629000</v>
+        <v>138022000</v>
       </c>
       <c r="AH2" t="n">
-        <v>65067000</v>
+        <v>28644000</v>
       </c>
       <c r="AI2" t="n">
-        <v>187138000</v>
+        <v>213514000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4468918000</v>
+        <v>4216464000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1348169000</v>
+        <v>1253278000</v>
       </c>
       <c r="AL2" t="n">
-        <v>12225000</v>
+        <v>14684000</v>
       </c>
       <c r="AM2" t="n">
-        <v>13489000</v>
+        <v>19407000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6982000</v>
+        <v>7484000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6982000</v>
+        <v>7484000</v>
       </c>
       <c r="AP2" t="n">
-        <v>144328000</v>
+        <v>108965000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>79726000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3152000</v>
+        <v>1553000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1167993000</v>
+        <v>1021459000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1167993000</v>
+        <v>1021459000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1167993000</v>
+        <v>1021459000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3120749000</v>
+        <v>2963186000</v>
       </c>
       <c r="AW2" t="n">
-        <v>4247000</v>
+        <v>1308000</v>
       </c>
       <c r="AX2" t="n">
-        <v>156773000</v>
+        <v>352113000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1763318000</v>
+        <v>1704991000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>82300000</v>
+        <v>93530000</v>
       </c>
       <c r="BA2" t="n">
-        <v>1587000</v>
+        <v>1556000</v>
       </c>
       <c r="BB2" t="n">
-        <v>443050000</v>
+        <v>513722000</v>
       </c>
       <c r="BC2" t="n">
-        <v>443050000</v>
+        <v>513722000</v>
       </c>
       <c r="BD2" t="n">
-        <v>669474000</v>
+        <v>295966000</v>
       </c>
       <c r="BE2" t="n">
-        <v>77125000</v>
+        <v>41236000</v>
       </c>
       <c r="BF2" t="n">
-        <v>592349000</v>
+        <v>254730000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>102098000</v>
@@ -1677,40 +1675,40 @@
         <v>102098000</v>
       </c>
       <c r="D3" t="n">
-        <v>1729486000</v>
+        <v>1312670000</v>
       </c>
       <c r="E3" t="n">
-        <v>2131435000</v>
+        <v>1817710000</v>
       </c>
       <c r="F3" t="n">
-        <v>2371510000</v>
+        <v>2329440000</v>
       </c>
       <c r="G3" t="n">
-        <v>4481350000</v>
+        <v>4140773000</v>
       </c>
       <c r="H3" t="n">
-        <v>1270392000</v>
+        <v>1239972000</v>
       </c>
       <c r="I3" t="n">
-        <v>2371510000</v>
+        <v>2329440000</v>
       </c>
       <c r="J3" t="n">
-        <v>26105000</v>
+        <v>10192000</v>
       </c>
       <c r="K3" t="n">
-        <v>2376020000</v>
+        <v>2333255000</v>
       </c>
       <c r="L3" t="n">
-        <v>2514664000</v>
+        <v>2481744000</v>
       </c>
       <c r="M3" t="n">
-        <v>2376020000</v>
+        <v>2333255000</v>
       </c>
       <c r="N3" t="n">
-        <v>2376020000</v>
+        <v>2333255000</v>
       </c>
       <c r="O3" t="n">
-        <v>797470000</v>
+        <v>764189000</v>
       </c>
       <c r="P3" t="n">
         <v>345544000</v>
@@ -1722,129 +1720,127 @@
         <v>1020982000</v>
       </c>
       <c r="S3" t="n">
-        <v>2597636000</v>
+        <v>2239288000</v>
       </c>
       <c r="T3" t="n">
-        <v>176749000</v>
+        <v>189664000</v>
       </c>
       <c r="U3" t="n">
-        <v>1299000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
+        <v>2509000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>14695000</v>
+        <v>29001000</v>
       </c>
       <c r="X3" t="n">
-        <v>160755000</v>
+        <v>158154000</v>
       </c>
       <c r="Y3" t="n">
-        <v>22111000</v>
+        <v>9665000</v>
       </c>
       <c r="Z3" t="n">
-        <v>138644000</v>
+        <v>148489000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2420887000</v>
+        <v>2049624000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1599000</v>
+        <v>3021000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1970680000</v>
+        <v>1659556000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3994000</v>
+        <v>527000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1966686000</v>
+        <v>1659029000</v>
       </c>
       <c r="AF3" t="n">
-        <v>430576000</v>
+        <v>369497000</v>
       </c>
       <c r="AG3" t="n">
-        <v>151793000</v>
+        <v>166907000</v>
       </c>
       <c r="AH3" t="n">
-        <v>50451000</v>
+        <v>55172000</v>
       </c>
       <c r="AI3" t="n">
-        <v>228332000</v>
+        <v>147418000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4973656000</v>
+        <v>4572543000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1282377000</v>
+        <v>1282947000</v>
       </c>
       <c r="AL3" t="n">
-        <v>65630000</v>
+        <v>66534000</v>
       </c>
       <c r="AM3" t="n">
-        <v>15399000</v>
+        <v>10916000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6982000</v>
+        <v>6900000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6982000</v>
+        <v>6900000</v>
       </c>
       <c r="AP3" t="n">
-        <v>116360000</v>
+        <v>108031000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>79182000</v>
+        <v>79454000</v>
       </c>
       <c r="AR3" t="n">
-        <v>4510000</v>
+        <v>3815000</v>
       </c>
       <c r="AS3" t="n">
-        <v>994314000</v>
+        <v>1007297000</v>
       </c>
       <c r="AT3" t="n">
-        <v>994314000</v>
+        <v>1007297000</v>
       </c>
       <c r="AU3" t="n">
-        <v>994314000</v>
+        <v>1007297000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3691279000</v>
+        <v>3289596000</v>
       </c>
       <c r="AW3" t="n">
-        <v>2042000</v>
+        <v>1861000</v>
       </c>
       <c r="AX3" t="n">
-        <v>191388000</v>
+        <v>152559000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2364809000</v>
+        <v>1827492000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>92214000</v>
+        <v>92510000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1484000</v>
+        <v>1537000</v>
       </c>
       <c r="BB3" t="n">
-        <v>584474000</v>
+        <v>652729000</v>
       </c>
       <c r="BC3" t="n">
-        <v>584474000</v>
+        <v>652729000</v>
       </c>
       <c r="BD3" t="n">
-        <v>454868000</v>
+        <v>560908000</v>
       </c>
       <c r="BE3" t="n">
-        <v>79024000</v>
+        <v>66060000</v>
       </c>
       <c r="BF3" t="n">
-        <v>375844000</v>
+        <v>494848000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>102098000</v>
@@ -1853,40 +1849,40 @@
         <v>102098000</v>
       </c>
       <c r="D4" t="n">
-        <v>1312670000</v>
+        <v>1729486000</v>
       </c>
       <c r="E4" t="n">
-        <v>1817710000</v>
+        <v>2131435000</v>
       </c>
       <c r="F4" t="n">
-        <v>2329440000</v>
+        <v>2371510000</v>
       </c>
       <c r="G4" t="n">
-        <v>4140773000</v>
+        <v>4481350000</v>
       </c>
       <c r="H4" t="n">
-        <v>1239972000</v>
+        <v>1270392000</v>
       </c>
       <c r="I4" t="n">
-        <v>2329440000</v>
+        <v>2371510000</v>
       </c>
       <c r="J4" t="n">
-        <v>10192000</v>
+        <v>26105000</v>
       </c>
       <c r="K4" t="n">
-        <v>2333255000</v>
+        <v>2376020000</v>
       </c>
       <c r="L4" t="n">
-        <v>2481744000</v>
+        <v>2514664000</v>
       </c>
       <c r="M4" t="n">
-        <v>2333255000</v>
+        <v>2376020000</v>
       </c>
       <c r="N4" t="n">
-        <v>2333255000</v>
+        <v>2376020000</v>
       </c>
       <c r="O4" t="n">
-        <v>764189000</v>
+        <v>797470000</v>
       </c>
       <c r="P4" t="n">
         <v>345544000</v>
@@ -1898,127 +1894,129 @@
         <v>1020982000</v>
       </c>
       <c r="S4" t="n">
-        <v>2239288000</v>
+        <v>2597636000</v>
       </c>
       <c r="T4" t="n">
-        <v>189664000</v>
+        <v>176749000</v>
       </c>
       <c r="U4" t="n">
-        <v>2509000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>1299000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" t="n">
-        <v>29001000</v>
+        <v>14695000</v>
       </c>
       <c r="X4" t="n">
-        <v>158154000</v>
+        <v>160755000</v>
       </c>
       <c r="Y4" t="n">
-        <v>9665000</v>
+        <v>22111000</v>
       </c>
       <c r="Z4" t="n">
-        <v>148489000</v>
+        <v>138644000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2049624000</v>
+        <v>2420887000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3021000</v>
+        <v>1599000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1659556000</v>
+        <v>1970680000</v>
       </c>
       <c r="AD4" t="n">
-        <v>527000</v>
+        <v>3994000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1659029000</v>
+        <v>1966686000</v>
       </c>
       <c r="AF4" t="n">
-        <v>369497000</v>
+        <v>430576000</v>
       </c>
       <c r="AG4" t="n">
-        <v>166907000</v>
+        <v>151793000</v>
       </c>
       <c r="AH4" t="n">
-        <v>55172000</v>
+        <v>50451000</v>
       </c>
       <c r="AI4" t="n">
-        <v>147418000</v>
+        <v>228332000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4572543000</v>
+        <v>4973656000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1282947000</v>
+        <v>1282377000</v>
       </c>
       <c r="AL4" t="n">
-        <v>66534000</v>
+        <v>65630000</v>
       </c>
       <c r="AM4" t="n">
-        <v>10916000</v>
+        <v>15399000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6900000</v>
+        <v>6982000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6900000</v>
+        <v>6982000</v>
       </c>
       <c r="AP4" t="n">
-        <v>108031000</v>
+        <v>116360000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>79454000</v>
+        <v>79182000</v>
       </c>
       <c r="AR4" t="n">
-        <v>3815000</v>
+        <v>4510000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1007297000</v>
+        <v>994314000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1007297000</v>
+        <v>994314000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1007297000</v>
+        <v>994314000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3289596000</v>
+        <v>3691279000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1861000</v>
+        <v>2042000</v>
       </c>
       <c r="AX4" t="n">
-        <v>152559000</v>
+        <v>191388000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1827492000</v>
+        <v>2364809000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>92510000</v>
+        <v>92214000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1537000</v>
+        <v>1484000</v>
       </c>
       <c r="BB4" t="n">
-        <v>652729000</v>
+        <v>584474000</v>
       </c>
       <c r="BC4" t="n">
-        <v>652729000</v>
+        <v>584474000</v>
       </c>
       <c r="BD4" t="n">
-        <v>560908000</v>
+        <v>454868000</v>
       </c>
       <c r="BE4" t="n">
-        <v>66060000</v>
+        <v>79024000</v>
       </c>
       <c r="BF4" t="n">
-        <v>494848000</v>
+        <v>375844000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>102098000</v>
@@ -2027,40 +2025,40 @@
         <v>102098000</v>
       </c>
       <c r="D5" t="n">
-        <v>1342591000</v>
+        <v>1070220000</v>
       </c>
       <c r="E5" t="n">
-        <v>1608028000</v>
+        <v>1687599000</v>
       </c>
       <c r="F5" t="n">
-        <v>2169690000</v>
+        <v>2316332000</v>
       </c>
       <c r="G5" t="n">
-        <v>3768564000</v>
+        <v>3982053000</v>
       </c>
       <c r="H5" t="n">
-        <v>1113195000</v>
+        <v>1126026000</v>
       </c>
       <c r="I5" t="n">
-        <v>2169690000</v>
+        <v>2316332000</v>
       </c>
       <c r="J5" t="n">
-        <v>10707000</v>
+        <v>25030000</v>
       </c>
       <c r="K5" t="n">
-        <v>2171243000</v>
+        <v>2319484000</v>
       </c>
       <c r="L5" t="n">
-        <v>2328604000</v>
+        <v>2448284000</v>
       </c>
       <c r="M5" t="n">
-        <v>2171243000</v>
+        <v>2319484000</v>
       </c>
       <c r="N5" t="n">
-        <v>2171243000</v>
+        <v>2319484000</v>
       </c>
       <c r="O5" t="n">
-        <v>634781000</v>
+        <v>687811000</v>
       </c>
       <c r="P5" t="n">
         <v>345544000</v>
@@ -2072,122 +2070,124 @@
         <v>1020982000</v>
       </c>
       <c r="S5" t="n">
-        <v>2045221000</v>
+        <v>2149434000</v>
       </c>
       <c r="T5" t="n">
-        <v>195230000</v>
+        <v>154711000</v>
       </c>
       <c r="U5" t="n">
-        <v>2476000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>1120000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1687000</v>
+      </c>
       <c r="W5" t="n">
-        <v>25201000</v>
+        <v>2721000</v>
       </c>
       <c r="X5" t="n">
-        <v>167553000</v>
+        <v>149183000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10192000</v>
+        <v>20383000</v>
       </c>
       <c r="Z5" t="n">
-        <v>157361000</v>
+        <v>128800000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1849991000</v>
+        <v>1994723000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2144000</v>
+        <v>1854000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1440475000</v>
+        <v>1538416000</v>
       </c>
       <c r="AD5" t="n">
-        <v>515000</v>
+        <v>4647000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1439960000</v>
+        <v>1533769000</v>
       </c>
       <c r="AF5" t="n">
-        <v>380180000</v>
+        <v>422834000</v>
       </c>
       <c r="AG5" t="n">
-        <v>138022000</v>
+        <v>170629000</v>
       </c>
       <c r="AH5" t="n">
-        <v>28644000</v>
+        <v>65067000</v>
       </c>
       <c r="AI5" t="n">
-        <v>213514000</v>
+        <v>187138000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4216464000</v>
+        <v>4468918000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1253278000</v>
+        <v>1348169000</v>
       </c>
       <c r="AL5" t="n">
-        <v>14684000</v>
+        <v>12225000</v>
       </c>
       <c r="AM5" t="n">
-        <v>19407000</v>
+        <v>13489000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7484000</v>
+        <v>6982000</v>
       </c>
       <c r="AO5" t="n">
-        <v>7484000</v>
+        <v>6982000</v>
       </c>
       <c r="AP5" t="n">
-        <v>108965000</v>
+        <v>144328000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>79726000</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1553000</v>
+        <v>3152000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1021459000</v>
+        <v>1167993000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1021459000</v>
+        <v>1167993000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1021459000</v>
+        <v>1167993000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2963186000</v>
+        <v>3120749000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1308000</v>
+        <v>4247000</v>
       </c>
       <c r="AX5" t="n">
-        <v>352113000</v>
+        <v>156773000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1704991000</v>
+        <v>1763318000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>93530000</v>
+        <v>82300000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1556000</v>
+        <v>1587000</v>
       </c>
       <c r="BB5" t="n">
-        <v>513722000</v>
+        <v>443050000</v>
       </c>
       <c r="BC5" t="n">
-        <v>513722000</v>
+        <v>443050000</v>
       </c>
       <c r="BD5" t="n">
-        <v>295966000</v>
+        <v>669474000</v>
       </c>
       <c r="BE5" t="n">
-        <v>41236000</v>
+        <v>77125000</v>
       </c>
       <c r="BF5" t="n">
-        <v>254730000</v>
+        <v>592349000</v>
       </c>
     </row>
   </sheetData>
@@ -2448,586 +2448,586 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>774801000</v>
+        <v>-261445000</v>
       </c>
       <c r="C2" t="n">
-        <v>-470427000</v>
+        <v>-11350000</v>
       </c>
       <c r="D2" t="n">
-        <v>20000000</v>
+        <v>214236000</v>
       </c>
       <c r="E2" t="n">
-        <v>-139124000</v>
+        <v>-65294000</v>
       </c>
       <c r="F2" t="n">
-        <v>592349000</v>
+        <v>254730000</v>
       </c>
       <c r="G2" t="n">
-        <v>375844000</v>
+        <v>371936000</v>
       </c>
       <c r="H2" t="n">
-        <v>4772000</v>
+        <v>2492000</v>
       </c>
       <c r="I2" t="n">
-        <v>211733000</v>
+        <v>-119698000</v>
       </c>
       <c r="J2" t="n">
-        <v>-567280000</v>
+        <v>125774000</v>
       </c>
       <c r="K2" t="n">
-        <v>-305000</v>
+        <v>-35000</v>
       </c>
       <c r="L2" t="n">
-        <v>-112308000</v>
+        <v>-76574000</v>
       </c>
       <c r="M2" t="n">
-        <v>-450427000</v>
+        <v>202886000</v>
       </c>
       <c r="N2" t="n">
-        <v>-440582000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>214236000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>20000000</v>
+        <v>214236000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9845000</v>
+        <v>-11350000</v>
       </c>
       <c r="R2" t="n">
-        <v>-9845000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>-11350000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
       <c r="T2" t="n">
-        <v>-134912000</v>
+        <v>-49321000</v>
       </c>
       <c r="U2" t="n">
-        <v>815000</v>
+        <v>3190000</v>
       </c>
       <c r="V2" t="n">
-        <v>1899000</v>
+        <v>11534000</v>
       </c>
       <c r="W2" t="n">
-        <v>80498000</v>
+        <v>37185000</v>
       </c>
       <c r="X2" t="n">
-        <v>-78599000</v>
+        <v>-25651000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-376000</v>
+        <v>-408000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-376000</v>
+        <v>-408000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-137250000</v>
+        <v>-63637000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1498000</v>
+        <v>1249000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-138748000</v>
+        <v>-64886000</v>
       </c>
       <c r="AD2" t="n">
-        <v>913925000</v>
+        <v>-196151000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-83720000</v>
+        <v>-24789000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2612000</v>
+        <v>614000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-80974000</v>
+        <v>-28760000</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>780288000</v>
+        <v>-531500000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>373000</v>
+        <v>3310000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5726000</v>
+        <v>14299000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-60109000</v>
+        <v>67761000</v>
       </c>
       <c r="AM2" t="n">
-        <v>50726000</v>
+        <v>-19175000</v>
       </c>
       <c r="AN2" t="n">
-        <v>636203000</v>
+        <v>-424583000</v>
       </c>
       <c r="AO2" t="n">
-        <v>158916000</v>
+        <v>-173112000</v>
       </c>
       <c r="AP2" t="n">
-        <v>78238000</v>
+        <v>27896000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-3309000</v>
+        <v>-1114000</v>
       </c>
       <c r="AR2" t="n">
-        <v>112742000</v>
+        <v>101578000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1802000</v>
+        <v>278000</v>
       </c>
       <c r="AT2" t="n">
-        <v>110940000</v>
+        <v>101300000</v>
       </c>
       <c r="AU2" t="n">
-        <v>996000</v>
+        <v>251000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3780000</v>
+        <v>646000</v>
       </c>
       <c r="AW2" t="n">
-        <v>115852000</v>
+        <v>271714000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-250353000</v>
+        <v>212442000</v>
       </c>
       <c r="C3" t="n">
-        <v>-9845000</v>
+        <v>-174572000</v>
       </c>
       <c r="D3" t="n">
-        <v>311485000</v>
+        <v>384738000</v>
       </c>
       <c r="E3" t="n">
-        <v>-85719000</v>
+        <v>-95967000</v>
       </c>
       <c r="F3" t="n">
-        <v>375844000</v>
+        <v>494848000</v>
       </c>
       <c r="G3" t="n">
-        <v>494848000</v>
+        <v>254730000</v>
       </c>
       <c r="H3" t="n">
-        <v>-4032000</v>
+        <v>-7091000</v>
       </c>
       <c r="I3" t="n">
-        <v>-114972000</v>
+        <v>247209000</v>
       </c>
       <c r="J3" t="n">
-        <v>147968000</v>
+        <v>97343000</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-153145000</v>
+        <v>-112308000</v>
       </c>
       <c r="M3" t="n">
-        <v>301640000</v>
+        <v>210166000</v>
       </c>
       <c r="N3" t="n">
-        <v>311485000</v>
+        <v>220661000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>311485000</v>
+        <v>220661000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9845000</v>
+        <v>-10495000</v>
       </c>
       <c r="R3" t="n">
-        <v>-9845000</v>
+        <v>-174572000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>164077000</v>
       </c>
       <c r="T3" t="n">
-        <v>-98306000</v>
+        <v>-158543000</v>
       </c>
       <c r="U3" t="n">
-        <v>128000</v>
+        <v>-39605000</v>
       </c>
       <c r="V3" t="n">
-        <v>-13046000</v>
+        <v>-24240000</v>
       </c>
       <c r="W3" t="n">
-        <v>22517000</v>
+        <v>56255000</v>
       </c>
       <c r="X3" t="n">
-        <v>-35563000</v>
+        <v>-80495000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1967000</v>
+        <v>-1358000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1967000</v>
+        <v>-1358000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-83421000</v>
+        <v>-93340000</v>
       </c>
       <c r="AB3" t="n">
-        <v>331000</v>
+        <v>1269000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-83752000</v>
+        <v>-94609000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-164634000</v>
+        <v>308409000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-81587000</v>
+        <v>-43852000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2499000</v>
+        <v>1558000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-69331000</v>
+        <v>-33703000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3525000</v>
+        <v>4402000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-450456000</v>
+        <v>-111520000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2431000</v>
+        <v>-1449000</v>
       </c>
       <c r="AK3" t="n">
-        <v>513000</v>
+        <v>-25176000</v>
       </c>
       <c r="AL3" t="n">
-        <v>72089000</v>
+        <v>-38646000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-21643000</v>
+        <v>196942000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-556822000</v>
+        <v>-104899000</v>
       </c>
       <c r="AO3" t="n">
-        <v>57838000</v>
+        <v>-138292000</v>
       </c>
       <c r="AP3" t="n">
-        <v>66891000</v>
+        <v>32617000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6789000</v>
+        <v>2177000</v>
       </c>
       <c r="AR3" t="n">
-        <v>105759000</v>
+        <v>104231000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1514000</v>
+        <v>677000</v>
       </c>
       <c r="AT3" t="n">
-        <v>104245000</v>
+        <v>103554000</v>
       </c>
       <c r="AU3" t="n">
-        <v>555000</v>
+        <v>1214000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2400000</v>
+        <v>66000</v>
       </c>
       <c r="AW3" t="n">
-        <v>264497000</v>
+        <v>346091000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>212442000</v>
+        <v>-250353000</v>
       </c>
       <c r="C4" t="n">
-        <v>-174572000</v>
+        <v>-9845000</v>
       </c>
       <c r="D4" t="n">
-        <v>384738000</v>
+        <v>311485000</v>
       </c>
       <c r="E4" t="n">
-        <v>-95967000</v>
+        <v>-85719000</v>
       </c>
       <c r="F4" t="n">
+        <v>375844000</v>
+      </c>
+      <c r="G4" t="n">
         <v>494848000</v>
       </c>
-      <c r="G4" t="n">
-        <v>254730000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-7091000</v>
+        <v>-4032000</v>
       </c>
       <c r="I4" t="n">
-        <v>247209000</v>
+        <v>-114972000</v>
       </c>
       <c r="J4" t="n">
-        <v>97343000</v>
+        <v>147968000</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-112308000</v>
+        <v>-153145000</v>
       </c>
       <c r="M4" t="n">
-        <v>210166000</v>
+        <v>301640000</v>
       </c>
       <c r="N4" t="n">
-        <v>220661000</v>
+        <v>311485000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>220661000</v>
+        <v>311485000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10495000</v>
+        <v>-9845000</v>
       </c>
       <c r="R4" t="n">
-        <v>-174572000</v>
+        <v>-9845000</v>
       </c>
       <c r="S4" t="n">
-        <v>164077000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-158543000</v>
+        <v>-98306000</v>
       </c>
       <c r="U4" t="n">
-        <v>-39605000</v>
+        <v>128000</v>
       </c>
       <c r="V4" t="n">
-        <v>-24240000</v>
+        <v>-13046000</v>
       </c>
       <c r="W4" t="n">
-        <v>56255000</v>
+        <v>22517000</v>
       </c>
       <c r="X4" t="n">
-        <v>-80495000</v>
+        <v>-35563000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1358000</v>
+        <v>-1967000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1358000</v>
+        <v>-1967000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-93340000</v>
+        <v>-83421000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1269000</v>
+        <v>331000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-94609000</v>
+        <v>-83752000</v>
       </c>
       <c r="AD4" t="n">
-        <v>308409000</v>
+        <v>-164634000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-43852000</v>
+        <v>-81587000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1558000</v>
+        <v>2499000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-33703000</v>
+        <v>-69331000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4402000</v>
+        <v>3525000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-111520000</v>
+        <v>-450456000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1449000</v>
+        <v>-2431000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-25176000</v>
+        <v>513000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-38646000</v>
+        <v>72089000</v>
       </c>
       <c r="AM4" t="n">
-        <v>196942000</v>
+        <v>-21643000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-104899000</v>
+        <v>-556822000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-138292000</v>
+        <v>57838000</v>
       </c>
       <c r="AP4" t="n">
-        <v>32617000</v>
+        <v>66891000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2177000</v>
+        <v>6789000</v>
       </c>
       <c r="AR4" t="n">
-        <v>104231000</v>
+        <v>105759000</v>
       </c>
       <c r="AS4" t="n">
-        <v>677000</v>
+        <v>1514000</v>
       </c>
       <c r="AT4" t="n">
-        <v>103554000</v>
+        <v>104245000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1214000</v>
+        <v>555000</v>
       </c>
       <c r="AV4" t="n">
-        <v>66000</v>
+        <v>2400000</v>
       </c>
       <c r="AW4" t="n">
-        <v>346091000</v>
+        <v>264497000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-261445000</v>
+        <v>774801000</v>
       </c>
       <c r="C5" t="n">
-        <v>-11350000</v>
+        <v>-470427000</v>
       </c>
       <c r="D5" t="n">
-        <v>214236000</v>
+        <v>20000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-65294000</v>
+        <v>-139124000</v>
       </c>
       <c r="F5" t="n">
-        <v>254730000</v>
+        <v>592349000</v>
       </c>
       <c r="G5" t="n">
-        <v>371936000</v>
+        <v>375844000</v>
       </c>
       <c r="H5" t="n">
-        <v>2492000</v>
+        <v>4772000</v>
       </c>
       <c r="I5" t="n">
-        <v>-119698000</v>
+        <v>211733000</v>
       </c>
       <c r="J5" t="n">
-        <v>125774000</v>
+        <v>-567280000</v>
       </c>
       <c r="K5" t="n">
-        <v>-35000</v>
+        <v>-305000</v>
       </c>
       <c r="L5" t="n">
-        <v>-76574000</v>
+        <v>-112308000</v>
       </c>
       <c r="M5" t="n">
-        <v>202886000</v>
+        <v>-450427000</v>
       </c>
       <c r="N5" t="n">
-        <v>214236000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+        <v>-440582000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>214236000</v>
+        <v>20000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-11350000</v>
+        <v>-9845000</v>
       </c>
       <c r="R5" t="n">
-        <v>-11350000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
+        <v>-9845000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-49321000</v>
+        <v>-134912000</v>
       </c>
       <c r="U5" t="n">
-        <v>3190000</v>
+        <v>815000</v>
       </c>
       <c r="V5" t="n">
-        <v>11534000</v>
+        <v>1899000</v>
       </c>
       <c r="W5" t="n">
-        <v>37185000</v>
+        <v>80498000</v>
       </c>
       <c r="X5" t="n">
-        <v>-25651000</v>
+        <v>-78599000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-408000</v>
+        <v>-376000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-408000</v>
+        <v>-376000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-63637000</v>
+        <v>-137250000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1249000</v>
+        <v>1498000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-64886000</v>
+        <v>-138748000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-196151000</v>
+        <v>913925000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-24789000</v>
+        <v>-83720000</v>
       </c>
       <c r="AF5" t="n">
-        <v>614000</v>
+        <v>2612000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-28760000</v>
+        <v>-80974000</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-531500000</v>
+        <v>780288000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3310000</v>
+        <v>373000</v>
       </c>
       <c r="AK5" t="n">
-        <v>14299000</v>
+        <v>-5726000</v>
       </c>
       <c r="AL5" t="n">
-        <v>67761000</v>
+        <v>-60109000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-19175000</v>
+        <v>50726000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-424583000</v>
+        <v>636203000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-173112000</v>
+        <v>158916000</v>
       </c>
       <c r="AP5" t="n">
-        <v>27896000</v>
+        <v>78238000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1114000</v>
+        <v>-3309000</v>
       </c>
       <c r="AR5" t="n">
-        <v>101578000</v>
+        <v>112742000</v>
       </c>
       <c r="AS5" t="n">
-        <v>278000</v>
+        <v>1802000</v>
       </c>
       <c r="AT5" t="n">
-        <v>101300000</v>
+        <v>110940000</v>
       </c>
       <c r="AU5" t="n">
-        <v>251000</v>
+        <v>996000</v>
       </c>
       <c r="AV5" t="n">
-        <v>646000</v>
+        <v>3780000</v>
       </c>
       <c r="AW5" t="n">
-        <v>271714000</v>
+        <v>115852000</v>
       </c>
     </row>
   </sheetData>
@@ -3572,172 +3572,172 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3839,34 +3839,34 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>24.55</v>
+        <v>23.5</v>
       </c>
       <c r="U2" t="n">
-        <v>23.45</v>
+        <v>23.5</v>
       </c>
       <c r="V2" t="n">
-        <v>23.25</v>
+        <v>23.35</v>
       </c>
       <c r="W2" t="n">
-        <v>24.35</v>
+        <v>24.65</v>
       </c>
       <c r="X2" t="n">
-        <v>24.55</v>
+        <v>23.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.45</v>
+        <v>23.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>23.25</v>
+        <v>23.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.35</v>
+        <v>24.65</v>
       </c>
       <c r="AB2" t="n">
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.57</v>
+        <v>8.35</v>
       </c>
       <c r="AD2" t="n">
         <v>1777420800</v>
@@ -3878,25 +3878,25 @@
         <v>4.31</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.197</v>
+        <v>0.142</v>
       </c>
       <c r="AH2" t="n">
-        <v>11.936275</v>
+        <v>12.083333</v>
       </c>
       <c r="AI2" t="n">
-        <v>33171</v>
+        <v>49171</v>
       </c>
       <c r="AJ2" t="n">
-        <v>33171</v>
+        <v>49171</v>
       </c>
       <c r="AK2" t="n">
-        <v>83056</v>
+        <v>85421</v>
       </c>
       <c r="AL2" t="n">
-        <v>67208</v>
+        <v>34331</v>
       </c>
       <c r="AM2" t="n">
-        <v>67208</v>
+        <v>34331</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3911,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2486086400</v>
+        <v>2516715776</v>
       </c>
       <c r="AS2" t="n">
-        <v>2394198100</v>
+        <v>2399303000</v>
       </c>
       <c r="AT2" t="n">
         <v>16.2</v>
@@ -3929,19 +3929,19 @@
         <v>12.787015</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.48083392</v>
+        <v>0.48675796</v>
       </c>
       <c r="AY2" t="n">
-        <v>24.672</v>
+        <v>24.799</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.91275</v>
+        <v>20.32525</v>
       </c>
       <c r="BA2" t="n">
         <v>2</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.08146639999999999</v>
+        <v>0.08510638</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -3952,13 +3952,13 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>3011591424</v>
+        <v>3042220800</v>
       </c>
       <c r="BF2" t="n">
         <v>0.040599998</v>
       </c>
       <c r="BG2" t="n">
-        <v>31742268</v>
+        <v>31640170</v>
       </c>
       <c r="BH2" t="n">
         <v>102098000</v>
@@ -3970,7 +3970,7 @@
         <v>24.714</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.9852715</v>
+        <v>0.9974103600000001</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -3996,16 +3996,16 @@
         <v>1503619200</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.582</v>
+        <v>0.588</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.813</v>
+        <v>7.893</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.17839193</v>
+        <v>0.21761656</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>2</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>24.35</v>
+        <v>24.65</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4118,131 +4118,131 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="b">
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>TWO</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_49215203</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Taipei</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>tw_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
         <v>0</v>
       </c>
-      <c r="DC2" t="b">
+      <c r="DI2" t="n">
+        <v>-0.14900017</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.0060083135</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>4.324749</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.21277715</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1782111545</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>FLAVOR</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Flavor Full Foods Inc.</t>
+        </is>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>1353891600000</v>
       </c>
-      <c r="DE2" t="n">
-        <v>-0.19999886</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>23.25 - 24.35</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Flavor Full Foods Inc.</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.8146593600000001</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1780383560</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>TWO</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_49215203</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Asia/Taipei</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>tw_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>FLAVOR</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DW2" t="n">
+        <v>1.1499996</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>23.35 - 24.65</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
         <is>
           <t>Taipei Exchange</t>
         </is>
       </c>
-      <c r="DV2" t="n">
-        <v>83056</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.5030864</v>
-      </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>85421</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>8.449999</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.52160484</v>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>16.2 - 31.2</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
-        <v>-6.8500004</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.2195513</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>17.839193</v>
-      </c>
-      <c r="EC2" t="n">
+      <c r="ED2" t="n">
+        <v>-6.550001</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.20993593</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>21.761656</v>
+      </c>
+      <c r="EG2" t="n">
         <v>2.04</v>
       </c>
-      <c r="ED2" t="n">
-        <v>-0.3220005</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.013051252</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>4.43725</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.22283462</v>
-      </c>
       <c r="EH2" t="n">
-        <v>20</v>
+        <v>4.8936152</v>
       </c>
       <c r="EI2" t="n">
-        <v>20</v>
+        <v>24.65</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
